--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -5387,12 +5387,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>fkilove</t>
+          <t>ace1331</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01080118915</t>
+          <t>01033906903</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>EDM_0502</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -5415,12 +5415,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ace1331</t>
+          <t>fkilove</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01033906903</t>
+          <t>01080118915</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EDM_0502</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -7151,22 +7151,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>kk_5009517640</t>
+          <t>kk_2770056564</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01090817520</t>
+          <t>01097609451</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7179,22 +7179,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_2770056564</t>
+          <t>kk_5009517640</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01097609451</t>
+          <t>01090817520</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -12331,12 +12331,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>kk_4611877390</t>
+          <t>kk_3440880252</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>01034010575</t>
+          <t>01023828239</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>demendgen</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
@@ -12359,12 +12359,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>kk_3440880252</t>
+          <t>kk_4611877390</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>01023828239</t>
+          <t>01034010575</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>demendgen</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
@@ -12751,22 +12751,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>kk_3181390163</t>
+          <t>kk_4486967764</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>01081430435</t>
+          <t>01095303556</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -12779,22 +12779,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>kk_4486967764</t>
+          <t>kk_3181390163</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>01095303556</t>
+          <t>01081430435</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -13507,12 +13507,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>kk_3866704464</t>
+          <t>kk_3377297415</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>01096848789</t>
+          <t>01088479524</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E468" t="inlineStr"/>
@@ -13535,12 +13535,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>kk_3377297415</t>
+          <t>kk_3866704464</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>01088479524</t>
+          <t>01096848789</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E469" t="inlineStr"/>
@@ -15635,12 +15635,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>youl29</t>
+          <t>kk_4602095632</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>01050134121</t>
+          <t>01033213747</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15663,12 +15663,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>kk_4602095632</t>
+          <t>youl29</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>01033213747</t>
+          <t>01050134121</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -16447,12 +16447,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>pjh5540</t>
+          <t>kk_4912807536</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>01085559978</t>
+          <t>01046055617</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>gdn</t>
         </is>
       </c>
       <c r="E573" t="inlineStr"/>
@@ -16475,12 +16475,12 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>kk_4912807536</t>
+          <t>pjh5540</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>01046055617</t>
+          <t>01085559978</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>gdn</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E574" t="inlineStr"/>
@@ -18099,22 +18099,22 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>kk_4705329623</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>01064926793</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E632" t="inlineStr"/>
@@ -18155,22 +18155,22 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>kk_4705329623</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01064926793</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E634" t="inlineStr"/>
@@ -19751,12 +19751,12 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>kk_4318436675</t>
+          <t>kk_3786745879</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>01031176390</t>
+          <t>01093675013</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E691" t="inlineStr"/>
@@ -19779,12 +19779,12 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>kk_3786745879</t>
+          <t>kk_4318436675</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>01093675013</t>
+          <t>01031176390</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E692" t="inlineStr"/>
@@ -19947,12 +19947,12 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4725433749</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01096687926</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E698" t="inlineStr"/>
@@ -19975,12 +19975,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>kk_4725433749</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>01096687926</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E699" t="inlineStr"/>
@@ -20003,12 +20003,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>kk_4455109384</t>
+          <t>kk_3911965677</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>01025222519</t>
+          <t>01029276124</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -20031,12 +20031,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>kk_3911965677</t>
+          <t>kk_4455109384</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>01029276124</t>
+          <t>01025222519</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -22103,22 +22103,22 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>kk_4857948457</t>
+          <t>lovelybeib</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>01058380760</t>
+          <t>01040981902</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E775" t="inlineStr"/>
@@ -22131,22 +22131,22 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>lovelybeib</t>
+          <t>kk_4857948457</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>01040981902</t>
+          <t>01058380760</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E776" t="inlineStr"/>
@@ -22411,12 +22411,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>sephira</t>
+          <t>jokowoo</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01041867593</t>
+          <t>01040299924</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -22426,7 +22426,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E786" t="inlineStr"/>
@@ -22439,12 +22439,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>jokowoo</t>
+          <t>sephira</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>01040299924</t>
+          <t>01041867593</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E787" t="inlineStr"/>
@@ -23615,12 +23615,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>kk_3179837389</t>
+          <t>kk_4582648301</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>01089490421</t>
+          <t>01040451815</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -23630,7 +23630,7 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>0803_SUMMER_LAST_CHANCE</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E829" t="inlineStr"/>
@@ -23643,12 +23643,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>kk_4582648301</t>
+          <t>kk_3179837389</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>01040451815</t>
+          <t>01089490421</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>0803_SUMMER_LAST_CHANCE</t>
         </is>
       </c>
       <c r="E830" t="inlineStr"/>
@@ -23783,12 +23783,12 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>kk_4604844467</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>01045678553</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E835" t="inlineStr"/>
@@ -23811,12 +23811,12 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>kk_4604844467</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01045678553</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E836" t="inlineStr"/>
@@ -24119,22 +24119,22 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>kk_4298043202</t>
+          <t>tesung1133</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>01047114486</t>
+          <t>01080018889</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
       <c r="E847" t="inlineStr"/>
@@ -24147,22 +24147,22 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>tesung1133</t>
+          <t>kk_4298043202</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>01080018889</t>
+          <t>01047114486</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E848" t="inlineStr"/>
@@ -24371,12 +24371,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>kk_4354536465</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>01090782401</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E856" t="inlineStr"/>
@@ -24399,12 +24399,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4354536465</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01090782401</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -24414,7 +24414,7 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E857" t="inlineStr"/>
@@ -24707,12 +24707,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>kk_3166693744</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01045579380</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -24735,12 +24735,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>kk_3166693744</t>
+          <t>kk_3809928726</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>01045579380</t>
+          <t>01079193871</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -25239,12 +25239,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>kk_4864045300</t>
+          <t>kk_4376700680</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>01089985309</t>
+          <t>01047096832</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0425_FAMILYSALE</t>
         </is>
       </c>
       <c r="E887" t="inlineStr"/>
@@ -25267,12 +25267,12 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>kk_4376700680</t>
+          <t>kk_4864045300</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>01047096832</t>
+          <t>01089985309</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -25282,7 +25282,7 @@
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0425_FAMILYSALE</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E888" t="inlineStr"/>
@@ -25491,22 +25491,22 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>kk_4977819786</t>
+          <t>kk_4286220576</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>01063257991</t>
+          <t>01053587782</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_200416_seasonoff</t>
         </is>
       </c>
       <c r="E896" t="inlineStr"/>
@@ -25519,22 +25519,22 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>kk_4286220576</t>
+          <t>kk_4977819786</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>01053587782</t>
+          <t>01063257991</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_seasonoff</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E897" t="inlineStr"/>
@@ -25631,12 +25631,12 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>kk_3957117484</t>
+          <t>khyoon99</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01042204013</t>
+          <t>01044153686</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E901" t="inlineStr"/>
@@ -25659,12 +25659,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>kk_2825498802</t>
+          <t>kk_3957117484</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01027817891</t>
+          <t>01042204013</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -25674,7 +25674,7 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E902" t="inlineStr"/>
@@ -25687,12 +25687,12 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>jhj95</t>
+          <t>kk_2825498802</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>01031240827</t>
+          <t>01027817891</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E903" t="inlineStr"/>
@@ -25715,12 +25715,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>khyoon99</t>
+          <t>jhj95</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>01044153686</t>
+          <t>01031240827</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -11603,22 +11603,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>jaeho86</t>
+          <t>aurora1530</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>01091199057</t>
+          <t>01090756922</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>EDM_0317</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -11631,22 +11631,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>aurora1530</t>
+          <t>jaeho86</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>01090756922</t>
+          <t>01091199057</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EDM_0317</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
@@ -12331,12 +12331,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>kk_3440880252</t>
+          <t>kk_4611877390</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>01023828239</t>
+          <t>01034010575</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>demendgen</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
@@ -12359,12 +12359,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>kk_4611877390</t>
+          <t>kk_3440880252</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>01034010575</t>
+          <t>01023828239</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>demendgen</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
@@ -12751,22 +12751,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>kk_4486967764</t>
+          <t>kk_3181390163</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>01095303556</t>
+          <t>01081430435</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -12779,22 +12779,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>kk_3181390163</t>
+          <t>kk_4486967764</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>01081430435</t>
+          <t>01095303556</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -13003,22 +13003,22 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>kk_3777466040</t>
+          <t>kk_4742048286</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>01088374115</t>
+          <t>01046424731</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -13031,22 +13031,22 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>kk_4742048286</t>
+          <t>kk_3777466040</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>01046424731</t>
+          <t>01088374115</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
@@ -13507,12 +13507,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>kk_3866704464</t>
+          <t>kk_3377297415</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>01096848789</t>
+          <t>01088479524</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E468" t="inlineStr"/>
@@ -13535,12 +13535,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>kk_3377297415</t>
+          <t>kk_3866704464</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>01088479524</t>
+          <t>01096848789</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E469" t="inlineStr"/>
@@ -14543,22 +14543,22 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>designjy</t>
+          <t>lha0509</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>01035455888</t>
+          <t>01099215769</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>EDM_0512</t>
         </is>
       </c>
       <c r="E505" t="inlineStr"/>
@@ -14571,22 +14571,22 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>lha0509</t>
+          <t>designjy</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>01099215769</t>
+          <t>01035455888</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>EDM_0512</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E506" t="inlineStr"/>
@@ -15635,12 +15635,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>youl29</t>
+          <t>kk_4602095632</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>01050134121</t>
+          <t>01033213747</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15663,12 +15663,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>kk_4602095632</t>
+          <t>youl29</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>01033213747</t>
+          <t>01050134121</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -16447,12 +16447,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>pjh5540</t>
+          <t>kk_4912807536</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>01085559978</t>
+          <t>01046055617</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>gdn</t>
         </is>
       </c>
       <c r="E573" t="inlineStr"/>
@@ -16475,12 +16475,12 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>kk_4912807536</t>
+          <t>pjh5540</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>01046055617</t>
+          <t>01085559978</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>gdn</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E574" t="inlineStr"/>
@@ -16643,22 +16643,22 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>kk_4709923210</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>01096124789</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E580" t="inlineStr"/>
@@ -16671,22 +16671,22 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_4709923210</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01096124789</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E581" t="inlineStr"/>
@@ -18099,12 +18099,12 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>kk_4705329623</t>
+          <t>kk_5002711068</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>01064926793</t>
+          <t>01091991969</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E632" t="inlineStr"/>
@@ -18127,22 +18127,22 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>kk_4705329623</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01064926793</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E633" t="inlineStr"/>
@@ -18155,22 +18155,22 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>kk_5002711068</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>01091991969</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E634" t="inlineStr"/>
@@ -18323,22 +18323,22 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>kk_3490560323</t>
+          <t>ing106</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>01035493044</t>
+          <t>01099047122</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0423_EFW</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E640" t="inlineStr"/>
@@ -18351,22 +18351,22 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>ing106</t>
+          <t>kk_3490560323</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>01099047122</t>
+          <t>01035493044</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_CH_MESSAGE_0423_EFW</t>
         </is>
       </c>
       <c r="E641" t="inlineStr"/>
@@ -19751,12 +19751,12 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>kk_3786745879</t>
+          <t>kk_4318436675</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>01093675013</t>
+          <t>01031176390</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E691" t="inlineStr"/>
@@ -19779,12 +19779,12 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>kk_4318436675</t>
+          <t>kk_3786745879</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>01031176390</t>
+          <t>01093675013</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E692" t="inlineStr"/>
@@ -19835,22 +19835,22 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E694" t="inlineStr"/>
@@ -19863,22 +19863,22 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E695" t="inlineStr"/>
@@ -20479,12 +20479,12 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>kk_4883722134</t>
+          <t>kk_4202144050</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>01043573603</t>
+          <t>01085708380</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0507_LIGHTBACKPACK</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E717" t="inlineStr"/>
@@ -20507,12 +20507,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>kk_4202144050</t>
+          <t>kk_4883722134</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>01085708380</t>
+          <t>01043573603</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0507_LIGHTBACKPACK</t>
         </is>
       </c>
       <c r="E718" t="inlineStr"/>
@@ -20675,22 +20675,22 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>kk_4747397154</t>
+          <t>cyclepm</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>01052568046</t>
+          <t>01027101838</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_1110_Raffle</t>
         </is>
       </c>
       <c r="E724" t="inlineStr"/>
@@ -20731,22 +20731,22 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>cyclepm</t>
+          <t>kk_4747397154</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>01027101838</t>
+          <t>01052568046</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>LMS_ECOM_1110_Raffle</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E726" t="inlineStr"/>
@@ -21907,22 +21907,22 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>silverjida</t>
+          <t>hunylee</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>01028180759</t>
+          <t>01086334375</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E768" t="inlineStr"/>
@@ -21935,22 +21935,22 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>hunylee</t>
+          <t>silverjida</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>01086334375</t>
+          <t>01028180759</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E769" t="inlineStr"/>
@@ -22411,12 +22411,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>sephira</t>
+          <t>jokowoo</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01041867593</t>
+          <t>01040299924</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -22426,7 +22426,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E786" t="inlineStr"/>
@@ -22439,12 +22439,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>jokowoo</t>
+          <t>sephira</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>01040299924</t>
+          <t>01041867593</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E787" t="inlineStr"/>
@@ -23531,22 +23531,22 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>kk_3295287343</t>
+          <t>kk_3691186788</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>01055787714</t>
+          <t>01072030738</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E826" t="inlineStr"/>
@@ -23559,22 +23559,22 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>kk_3691186788</t>
+          <t>kk_3295287343</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>01072030738</t>
+          <t>01055787714</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E827" t="inlineStr"/>
@@ -23615,12 +23615,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>kk_3179837389</t>
+          <t>kk_4582648301</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>01089490421</t>
+          <t>01040451815</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -23630,7 +23630,7 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>0803_SUMMER_LAST_CHANCE</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E829" t="inlineStr"/>
@@ -23643,12 +23643,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>kk_4582648301</t>
+          <t>kk_3179837389</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>01040451815</t>
+          <t>01089490421</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>0803_SUMMER_LAST_CHANCE</t>
         </is>
       </c>
       <c r="E830" t="inlineStr"/>
@@ -23783,12 +23783,12 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>kk_4604844467</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>01045678553</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E835" t="inlineStr"/>
@@ -23811,12 +23811,12 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>kk_4604844467</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01045678553</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E836" t="inlineStr"/>
@@ -24119,22 +24119,22 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>tesung1133</t>
+          <t>kk_4298043202</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>01080018889</t>
+          <t>01047114486</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E847" t="inlineStr"/>
@@ -24147,22 +24147,22 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>kk_4298043202</t>
+          <t>tesung1133</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>01047114486</t>
+          <t>01080018889</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
       <c r="E848" t="inlineStr"/>
@@ -24287,22 +24287,22 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>uok77</t>
+          <t>ohjeong2</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>01089602950</t>
+          <t>01034324152</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0507_EFW_STYLE2</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E853" t="inlineStr"/>
@@ -24315,22 +24315,22 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>ohjeong2</t>
+          <t>uok77</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>01034324152</t>
+          <t>01089602950</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_CH_MESSAGE_0507_EFW_STYLE2</t>
         </is>
       </c>
       <c r="E854" t="inlineStr"/>
@@ -24371,12 +24371,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>kk_4354536465</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>01090782401</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E856" t="inlineStr"/>
@@ -24399,12 +24399,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4354536465</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01090782401</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -24414,7 +24414,7 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E857" t="inlineStr"/>
@@ -24511,12 +24511,12 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>leeyh015</t>
+          <t>kk_4614679325</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>01020785413</t>
+          <t>01063402986</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E861" t="inlineStr"/>
@@ -24539,12 +24539,12 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>kk_4614679325</t>
+          <t>leeyh015</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>01063402986</t>
+          <t>01020785413</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E862" t="inlineStr"/>
@@ -24623,22 +24623,22 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_2771972168</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01029820030</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E865" t="inlineStr"/>
@@ -24651,22 +24651,22 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>kk_2771972168</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>01029820030</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E866" t="inlineStr"/>
@@ -25491,22 +25491,22 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>kk_4286220576</t>
+          <t>kk_4977819786</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>01053587782</t>
+          <t>01063257991</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_seasonoff</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E896" t="inlineStr"/>
@@ -25519,22 +25519,22 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>kk_4977819786</t>
+          <t>kk_4286220576</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>01063257991</t>
+          <t>01053587782</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_200416_seasonoff</t>
         </is>
       </c>
       <c r="E897" t="inlineStr"/>
@@ -25631,12 +25631,12 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>khyoon99</t>
+          <t>kk_2825498802</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01044153686</t>
+          <t>01027817891</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E901" t="inlineStr"/>
@@ -25659,12 +25659,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>kk_3957117484</t>
+          <t>jhj95</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01042204013</t>
+          <t>01031240827</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -25674,7 +25674,7 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E902" t="inlineStr"/>
@@ -25687,12 +25687,12 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>kk_2825498802</t>
+          <t>kk_3957117484</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>01027817891</t>
+          <t>01042204013</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E903" t="inlineStr"/>
@@ -25715,12 +25715,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>jhj95</t>
+          <t>khyoon99</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>01031240827</t>
+          <t>01044153686</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -25827,12 +25827,12 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>tae12080</t>
+          <t>kk_3467972511</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>01093170063</t>
+          <t>01031899111</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E908" t="inlineStr"/>
@@ -25855,12 +25855,12 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>kk_3467972511</t>
+          <t>tae12080</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>01031899111</t>
+          <t>01093170063</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E909" t="inlineStr"/>

--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -515,12 +515,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>inhip</t>
+          <t>gbj20022002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01027705324</t>
+          <t>01053509041</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -543,22 +543,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_2873136069</t>
+          <t>merhen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01048866068</t>
+          <t>01025129134</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -571,22 +571,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_3864149982</t>
+          <t>inhip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01025551942</t>
+          <t>01027705324</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KAKAO_FridnsTalk_CartSale</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -599,22 +599,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_3433423317</t>
+          <t>kk_2873136069</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01075326556</t>
+          <t>01048866068</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -627,22 +627,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cool2vs2</t>
+          <t>kk_3864149982</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01027216492</t>
+          <t>01025551942</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>KAKAO_FridnsTalk_CartSale</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -655,22 +655,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4293495304</t>
+          <t>kk_3433423317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01032960676</t>
+          <t>01075326556</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -683,22 +683,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tjsgksrlf123</t>
+          <t>cool2vs2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01033775889</t>
+          <t>01027216492</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EDM_0126_bestreview</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -711,22 +711,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4446330406</t>
+          <t>kk_4293495304</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01027816365</t>
+          <t>01032960676</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -739,12 +739,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>magazz</t>
+          <t>tjsgksrlf123</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01099409643</t>
+          <t>01033775889</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EDM_0126_bestreview</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -767,22 +767,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_4209546622</t>
+          <t>kk_4446330406</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01079193288</t>
+          <t>01027816365</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -795,12 +795,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>speedking</t>
+          <t>magazz</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01051344025</t>
+          <t>01099409643</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -823,22 +823,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jhoh55555</t>
+          <t>kk_4209546622</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01062626688</t>
+          <t>01079193288</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -851,22 +851,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hennessy</t>
+          <t>speedking</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01030027773</t>
+          <t>01051344025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -879,22 +879,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_3803973742</t>
+          <t>jhoh55555</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01062581642</t>
+          <t>01062626688</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -907,22 +907,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>psw242</t>
+          <t>hennessy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01054125832</t>
+          <t>01030027773</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -935,22 +935,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_3243338539</t>
+          <t>kk_3803973742</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01025098649</t>
+          <t>01062581642</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -963,22 +963,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_4793170858</t>
+          <t>psw242</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01077026417</t>
+          <t>01054125832</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -991,22 +991,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jsy90</t>
+          <t>kk_3243338539</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01025098649</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1019,22 +1019,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>arrtieom</t>
+          <t>kk_4793170858</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01071593949</t>
+          <t>01077026417</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0521_BAHAMA1</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1047,12 +1047,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4778273271</t>
+          <t>jsy90</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01029527548</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1075,12 +1075,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>eastrain9</t>
+          <t>arrtieom</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01071445034</t>
+          <t>01071593949</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EDM</t>
+          <t>KAKAO_CH_MESSAGE_0521_BAHAMA1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1103,12 +1103,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>greom73</t>
+          <t>kk_4778273271</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01086372526</t>
+          <t>01029527548</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1131,22 +1131,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gidongi</t>
+          <t>eastrain9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01064373200</t>
+          <t>01071445034</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1159,12 +1159,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4323824634</t>
+          <t>greom73</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01021939477</t>
+          <t>01086372526</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1187,22 +1187,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>skku2738</t>
+          <t>gidongi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01074152738</t>
+          <t>01064373200</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1215,12 +1215,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chan680</t>
+          <t>kk_4323824634</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01026244284</t>
+          <t>01021939477</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1243,22 +1243,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4276234081</t>
+          <t>skku2738</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01046630168</t>
+          <t>01074152738</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1271,22 +1271,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>jhyeon41</t>
+          <t>chan680</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01038106019</t>
+          <t>01026244284</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1299,12 +1299,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_2826785228</t>
+          <t>kk_4276234081</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01022372658</t>
+          <t>01046630168</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1327,22 +1327,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_3511421009</t>
+          <t>jhyeon41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01031496540</t>
+          <t>01038106019</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1355,12 +1355,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4806290091</t>
+          <t>kk_2826785228</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01042848444</t>
+          <t>01022372658</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1383,22 +1383,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>serica22</t>
+          <t>kk_3511421009</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01095513653</t>
+          <t>01031496540</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0705_SEASON_OFF_2ND</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1411,22 +1411,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>kk_4806290091</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01042848444</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1439,22 +1439,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_3178599665</t>
+          <t>serica22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01089430429</t>
+          <t>01095513653</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>0705_SEASON_OFF_2ND</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1467,22 +1467,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ysc1111</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01041763874</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1495,12 +1495,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_3959240760</t>
+          <t>kk_3178599665</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01035045875</t>
+          <t>01089430429</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1523,12 +1523,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_3097873244</t>
+          <t>ysc1111</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01032060915</t>
+          <t>01041763874</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1551,12 +1551,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>alonzo22</t>
+          <t>kk_3959240760</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01062838804</t>
+          <t>01035045875</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1579,22 +1579,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_3746984520</t>
+          <t>kk_3097873244</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01029951804</t>
+          <t>01032060915</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1607,12 +1607,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_3895206189</t>
+          <t>alonzo22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01043980107</t>
+          <t>01062838804</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1635,22 +1635,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>k8017544</t>
+          <t>kk_3746984520</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01095772982</t>
+          <t>01029951804</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1663,22 +1663,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4745169563</t>
+          <t>kk_3895206189</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01047026526</t>
+          <t>01043980107</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>nap_new_members</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1691,22 +1691,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>djak0712</t>
+          <t>k8017544</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01063559841</t>
+          <t>01095772982</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1719,22 +1719,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>gunnie234</t>
+          <t>kk_4745169563</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01099652641</t>
+          <t>01047026526</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>nap_new_members</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1747,17 +1747,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4946126994</t>
+          <t>djak0712</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01055149084</t>
+          <t>01063559841</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1775,22 +1775,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>gunnie234</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01099652641</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1803,12 +1803,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>oshibun</t>
+          <t>kk_4946126994</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01029500259</t>
+          <t>01055149084</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1831,22 +1831,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_3042011585</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01073685152</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1859,22 +1859,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>passion1984</t>
+          <t>oshibun</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01064630333</t>
+          <t>01029500259</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1887,12 +1887,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sagepcs</t>
+          <t>kk_3042011585</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01058583300</t>
+          <t>01073685152</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1915,22 +1915,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_3297935659</t>
+          <t>passion1984</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01090281747</t>
+          <t>01064630333</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1943,17 +1943,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4656100370</t>
+          <t>sagepcs</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01091056580</t>
+          <t>01058583300</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1971,12 +1971,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_3840423259</t>
+          <t>kk_3297935659</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01050355480</t>
+          <t>01090281747</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>pmax</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -1999,12 +1999,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>redblood271</t>
+          <t>kk_4656100370</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01031572135</t>
+          <t>01091056580</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2027,12 +2027,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_5034001705</t>
+          <t>kk_3840423259</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01090601731</t>
+          <t>01050355480</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2055,22 +2055,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_3224620899</t>
+          <t>redblood271</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01085627400</t>
+          <t>01031572135</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2083,22 +2083,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kkhgreen</t>
+          <t>kk_5034001705</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01092780969</t>
+          <t>01090601731</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2111,12 +2111,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4319428238</t>
+          <t>kk_3224620899</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01092785785</t>
+          <t>01085627400</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2139,12 +2139,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_3941500642</t>
+          <t>kkhgreen</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01074450002</t>
+          <t>01092780969</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2167,12 +2167,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>beki76</t>
+          <t>kk_4319428238</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01088004778</t>
+          <t>01092785785</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2195,22 +2195,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>pck490210</t>
+          <t>kk_3941500642</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01025491031</t>
+          <t>01074450002</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2223,22 +2223,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>matmata</t>
+          <t>beki76</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01084207951</t>
+          <t>01088004778</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2251,12 +2251,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_3977151705</t>
+          <t>pck490210</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01025952746</t>
+          <t>01025491031</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2279,12 +2279,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>terran1123</t>
+          <t>matmata</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01053324395</t>
+          <t>01084207951</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2307,22 +2307,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_3977151705</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01025952746</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2335,22 +2335,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bbijim</t>
+          <t>terran1123</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01086676776</t>
+          <t>01053324395</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2363,12 +2363,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3297492631</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01022470507</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2391,22 +2391,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rudalsla</t>
+          <t>bbijim</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01071949782</t>
+          <t>01086676776</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2419,12 +2419,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>cubewheel</t>
+          <t>kk_3297492631</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01089546320</t>
+          <t>01022470507</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2447,22 +2447,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>rudalsla</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01071949782</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2475,12 +2475,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4991395508</t>
+          <t>cubewheel</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01025638959</t>
+          <t>01089546320</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2503,22 +2503,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_2988538598</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01055855280</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2531,22 +2531,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_3180798849</t>
+          <t>kk_4991395508</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01086259207</t>
+          <t>01025638959</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2559,22 +2559,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_3949933982</t>
+          <t>kk_2988538598</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01026968241</t>
+          <t>01055855280</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2587,12 +2587,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gitae76</t>
+          <t>kk_3180798849</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01020801107</t>
+          <t>01086259207</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2615,12 +2615,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_3182573827</t>
+          <t>kk_3949933982</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01077419077</t>
+          <t>01026968241</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2643,12 +2643,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>wodl8077</t>
+          <t>gitae76</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01097558077</t>
+          <t>01020801107</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2671,22 +2671,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>prologic</t>
+          <t>kk_3182573827</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01090864344</t>
+          <t>01077419077</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2699,12 +2699,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4863256269</t>
+          <t>wodl8077</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01027382913</t>
+          <t>01097558077</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2727,12 +2727,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>insangpa72</t>
+          <t>prologic</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01053035171</t>
+          <t>01090864344</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2755,12 +2755,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bjh4895</t>
+          <t>kk_4863256269</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01042374895</t>
+          <t>01027382913</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2783,22 +2783,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kjjopen</t>
+          <t>insangpa72</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01086035744</t>
+          <t>01053035171</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -2811,22 +2811,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3425319183</t>
+          <t>bjh4895</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01073728534</t>
+          <t>01042374895</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2839,22 +2839,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>blackout9</t>
+          <t>kjjopen</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01054444345</t>
+          <t>01086035744</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -2867,12 +2867,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>kk_3425319183</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01073728534</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2895,22 +2895,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_3522301091</t>
+          <t>blackout9</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01088731863</t>
+          <t>01054444345</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2923,12 +2923,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2951,12 +2951,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>garfield98</t>
+          <t>kk_3522301091</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01032643963</t>
+          <t>01088731863</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2979,12 +2979,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3007,12 +3007,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4355884570</t>
+          <t>garfield98</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01052096279</t>
+          <t>01032643963</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3035,22 +3035,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4785141094</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01022106967</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3063,22 +3063,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>king1090</t>
+          <t>kk_4355884570</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01064003306</t>
+          <t>01052096279</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3091,22 +3091,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mo21613</t>
+          <t>kk_4785141094</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01063041255</t>
+          <t>01022106967</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3119,22 +3119,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>johun0414</t>
+          <t>king1090</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01082150607</t>
+          <t>01064003306</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3147,17 +3147,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4313489248</t>
+          <t>mo21613</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01026591380</t>
+          <t>01063041255</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3175,22 +3175,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_3781116310</t>
+          <t>johun0414</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01052721277</t>
+          <t>01082150607</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3203,12 +3203,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>gun9670</t>
+          <t>kk_4313489248</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01051514803</t>
+          <t>01026591380</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3231,22 +3231,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_3781116310</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01052721277</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3259,12 +3259,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_3941904586</t>
+          <t>gun9670</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01067078239</t>
+          <t>01051514803</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3287,12 +3287,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4993751323</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01053138487</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3315,12 +3315,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_3478853991</t>
+          <t>kk_3941904586</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01077662474</t>
+          <t>01067078239</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -3343,12 +3343,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_3738826876</t>
+          <t>kk_4993751323</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01095514239</t>
+          <t>01053138487</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3371,12 +3371,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>hg1890</t>
+          <t>kk_3478853991</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01038436423</t>
+          <t>01077662474</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3399,12 +3399,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>hiwoong76</t>
+          <t>kk_3738826876</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01067981478</t>
+          <t>01095514239</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3427,12 +3427,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_3225675516</t>
+          <t>hg1890</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01022881015</t>
+          <t>01038436423</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>EDM_0226</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3455,12 +3455,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>nbhfrancisco</t>
+          <t>hiwoong76</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01050977100</t>
+          <t>01067981478</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>EDM</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -3483,12 +3483,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4678957107</t>
+          <t>kk_3225675516</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01034388709</t>
+          <t>01022881015</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>EDM_0226</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3511,22 +3511,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>jung03</t>
+          <t>nbhfrancisco</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01026209151</t>
+          <t>01050977100</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>EDM</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3539,22 +3539,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>yoichi</t>
+          <t>kk_4678957107</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01072692907</t>
+          <t>01034388709</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3567,22 +3567,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_3933214484</t>
+          <t>jung03</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01090832304</t>
+          <t>01026209151</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3595,12 +3595,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4940441538</t>
+          <t>yoichi</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01089269967</t>
+          <t>01072692907</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3623,12 +3623,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kk_3933214484</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01090832304</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3651,22 +3651,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_3240277946</t>
+          <t>kk_4940441538</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01049229190</t>
+          <t>01089269967</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3679,12 +3679,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4727133236</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01064755009</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[PF]전환_신상품 카탈로그(1865,관심사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3707,22 +3707,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>nayuna1022</t>
+          <t>kk_3240277946</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01062175214</t>
+          <t>01049229190</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3735,12 +3735,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>kk_4727133236</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01064755009</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_신상품 카탈로그(1865,관심사)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3763,22 +3763,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>nayuna1022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01062175214</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3791,22 +3791,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>yjookim67</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01054114855</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -3819,22 +3819,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>camha</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01031331918</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -3847,22 +3847,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>dawonint</t>
+          <t>yjookim67</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01037690185</t>
+          <t>01054114855</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -3875,12 +3875,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>camha</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01031331918</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -3903,22 +3903,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_5008721553</t>
+          <t>dawonint</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01089905677</t>
+          <t>01037690185</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -3931,22 +3931,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>jswoo99</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01031705383</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -3959,22 +3959,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_3179544090</t>
+          <t>kk_5008721553</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01095352220</t>
+          <t>01089905677</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -3987,22 +3987,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4796376423</t>
+          <t>jswoo99</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01035771357</t>
+          <t>01031705383</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -4015,22 +4015,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_3363127172</t>
+          <t>kk_3179544090</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01072739372</t>
+          <t>01095352220</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -4043,12 +4043,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4804817546</t>
+          <t>kk_4796376423</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01048111806</t>
+          <t>01035771357</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -4071,22 +4071,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4929674815</t>
+          <t>kk_3363127172</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01075264562</t>
+          <t>01072739372</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -4099,22 +4099,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>his9742</t>
+          <t>kk_4804817546</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01024949742</t>
+          <t>01048111806</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -4127,22 +4127,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ils1706</t>
+          <t>kk_4929674815</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01037004519</t>
+          <t>01075264562</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -4155,22 +4155,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_3477586140</t>
+          <t>his9742</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01066698868</t>
+          <t>01024949742</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -4183,12 +4183,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>jklee1316</t>
+          <t>ils1706</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01023358588</t>
+          <t>01037004519</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -4211,22 +4211,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_3778944759</t>
+          <t>kk_3477586140</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01066975193</t>
+          <t>01066698868</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -4239,22 +4239,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ino326</t>
+          <t>jklee1316</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01024921837</t>
+          <t>01023358588</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -4267,12 +4267,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4378858812_2</t>
+          <t>kk_3778944759</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01090939890</t>
+          <t>01066975193</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_1128_WINTERFESTIVAL_CTA</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -4295,22 +4295,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4300806197</t>
+          <t>ino326</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01045551631</t>
+          <t>01024921837</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -4323,12 +4323,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4880545805</t>
+          <t>kk_4378858812_2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01022237436</t>
+          <t>01090939890</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_1128_WINTERFESTIVAL_CTA</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4351,12 +4351,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>by5500</t>
+          <t>kk_4300806197</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01071770101</t>
+          <t>01045551631</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>EDM_0317</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4379,12 +4379,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3246810283</t>
+          <t>kk_4880545805</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01039315369</t>
+          <t>01022237436</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -4407,22 +4407,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>show5430</t>
+          <t>by5500</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01099500131</t>
+          <t>01071770101</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_0317</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4435,22 +4435,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>xcable</t>
+          <t>kk_3246810283</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01080043359</t>
+          <t>01039315369</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4463,12 +4463,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>lsu3080</t>
+          <t>show5430</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01068283080</t>
+          <t>01099500131</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4491,22 +4491,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_2762161146</t>
+          <t>xcable</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01046533615</t>
+          <t>01080043359</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LMS_ECOM_GnR</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4519,22 +4519,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_3212536253</t>
+          <t>lsu3080</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01097992453</t>
+          <t>01068283080</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4547,12 +4547,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_2762161146</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01046533615</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_GnR</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -4575,12 +4575,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>policejs</t>
+          <t>kk_3212536253</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01041704743</t>
+          <t>01097992453</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -4603,12 +4603,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>jpm111</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01029304010</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -4631,22 +4631,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>hajd1011</t>
+          <t>policejs</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01054401373</t>
+          <t>01041704743</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4659,22 +4659,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>yksik0528</t>
+          <t>jpm111</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01033992431</t>
+          <t>01029304010</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -4687,22 +4687,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4693581167</t>
+          <t>hajd1011</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01050127862</t>
+          <t>01054401373</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -4715,22 +4715,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4881694655</t>
+          <t>yksik0528</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01072580898</t>
+          <t>01033992431</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -4743,22 +4743,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4702753709</t>
+          <t>kk_4693581167</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01076663512</t>
+          <t>01050127862</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -4771,12 +4771,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>net1122</t>
+          <t>kk_4881694655</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01040964937</t>
+          <t>01072580898</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -4799,12 +4799,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4927707365</t>
+          <t>kk_4702753709</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01053829303</t>
+          <t>01076663512</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -4827,12 +4827,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>koreankim</t>
+          <t>net1122</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01095372588</t>
+          <t>01040964937</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -4855,12 +4855,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_3181446328</t>
+          <t>kk_4927707365</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01086441161</t>
+          <t>01053829303</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -4883,12 +4883,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>koreankim</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01095372588</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4911,12 +4911,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4360429720</t>
+          <t>kk_3181446328</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01089099036</t>
+          <t>01086441161</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -4939,12 +4939,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -4967,12 +4967,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_4703845503</t>
+          <t>kk_4360429720</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01057372401</t>
+          <t>01089099036</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -4995,12 +4995,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_3763845552</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01095701533</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5023,22 +5023,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>luvieye123</t>
+          <t>kk_4703845503</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01035949045</t>
+          <t>01057372401</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5051,22 +5051,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>pooo1228</t>
+          <t>kk_3763845552</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01062724056</t>
+          <t>01095701533</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5079,22 +5079,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_3380720822</t>
+          <t>luvieye123</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01054705220</t>
+          <t>01035949045</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -5107,12 +5107,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_3305072060</t>
+          <t>pooo1228</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01085390140</t>
+          <t>01062724056</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,논타겟)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -5135,12 +5135,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_4409064497</t>
+          <t>kk_3380720822</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01057371727</t>
+          <t>01054705220</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -5163,12 +5163,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4430409947</t>
+          <t>kk_3305072060</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01047358234</t>
+          <t>01085390140</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]A SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -5191,22 +5191,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>lefy</t>
+          <t>kk_4409064497</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01022414020</t>
+          <t>01057371727</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -5219,22 +5219,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>varkala1</t>
+          <t>kk_4430409947</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01080276669</t>
+          <t>01047358234</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -5247,22 +5247,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>njp0710</t>
+          <t>lefy</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01027282087</t>
+          <t>01022414020</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0610</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -5275,12 +5275,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>varkala1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01080276669</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5303,12 +5303,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>cshc</t>
+          <t>njp0710</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01053437643</t>
+          <t>01027282087</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>0610</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -5331,22 +5331,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>thebebob</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01094365308</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -5359,12 +5359,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_3794046073</t>
+          <t>cshc</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01056918495</t>
+          <t>01053437643</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5387,22 +5387,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>fkilove</t>
+          <t>thebebob</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01080118915</t>
+          <t>01094365308</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -5415,12 +5415,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ace1331</t>
+          <t>kk_3794046073</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01033906903</t>
+          <t>01056918495</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EDM_0502</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -5443,12 +5443,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>zxcvziii</t>
+          <t>ace1331</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01048169121</t>
+          <t>01033906903</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0502</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -5471,12 +5471,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4507190107</t>
+          <t>fkilove</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01091780704</t>
+          <t>01080118915</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -5499,12 +5499,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>zxcvziii</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01048169121</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -5527,22 +5527,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4461497985</t>
+          <t>kk_4507190107</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01063241461</t>
+          <t>01091780704</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -5555,12 +5555,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4739241016</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01082593038</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>nap_new_members</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -5583,22 +5583,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>kk_4461497985</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01063241461</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -5611,22 +5611,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ckddus2</t>
+          <t>kk_4739241016</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01048722142</t>
+          <t>01082593038</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>MOhomelink</t>
+          <t>nap_new_members</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -5639,12 +5639,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>juks2761</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01062646133</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0129</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -5667,12 +5667,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4659940912</t>
+          <t>ckddus2</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01041612810</t>
+          <t>01048722142</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>MOhomelink</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -5695,12 +5695,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>jyjangcti</t>
+          <t>juks2761</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01029378908</t>
+          <t>01062646133</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>EDM_0512</t>
+          <t>LMS_ECOM_0129</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -5723,22 +5723,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>rao2001</t>
+          <t>kk_4659940912</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01025653293</t>
+          <t>01041612810</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -5751,22 +5751,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>jyjangcti</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01063315178</t>
+          <t>01029378908</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_0512</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -5779,12 +5779,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>bong9ya</t>
+          <t>rao2001</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01045637364</t>
+          <t>01025653293</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -5807,12 +5807,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>lcs3017</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01094123017</t>
+          <t>01063315178</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -5835,12 +5835,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ljw855</t>
+          <t>bong9ya</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01041724332</t>
+          <t>01045637364</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -5863,22 +5863,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>amistrong</t>
+          <t>lcs3017</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01055097870</t>
+          <t>01094123017</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -5891,22 +5891,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>boxyogo</t>
+          <t>ljw855</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01047175275</t>
+          <t>01041724332</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -5919,22 +5919,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_4711669963</t>
+          <t>amistrong</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01053480904</t>
+          <t>01055097870</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -5947,22 +5947,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_3626975387</t>
+          <t>boxyogo</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01088796035</t>
+          <t>01047175275</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -5975,22 +5975,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_3100841256</t>
+          <t>kk_4711669963</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01054473961</t>
+          <t>01053480904</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -6003,12 +6003,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4339204533</t>
+          <t>kk_3626975387</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01064869716</t>
+          <t>01088796035</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -6031,12 +6031,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_4826700021</t>
+          <t>kk_3100841256</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01066078107</t>
+          <t>01054473961</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -6059,12 +6059,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_4240554258</t>
+          <t>kk_4339204533</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01035989843</t>
+          <t>01064869716</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -6087,22 +6087,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4826700021</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01066078107</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -6115,22 +6115,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>darius27</t>
+          <t>kk_4240554258</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01091911224</t>
+          <t>01035989843</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -6143,12 +6143,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>dimejin</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01086058650</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -6171,12 +6171,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>kjh30201236</t>
+          <t>darius27</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01030204946</t>
+          <t>01091911224</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -6199,12 +6199,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_2847176143</t>
+          <t>dimejin</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01038261331</t>
+          <t>01086058650</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6227,12 +6227,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_3170960220</t>
+          <t>kjh30201236</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01087729278</t>
+          <t>01030204946</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -6255,22 +6255,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_4748122429</t>
+          <t>kk_2847176143</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01089229240</t>
+          <t>01038261331</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -6283,22 +6283,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_4545437798</t>
+          <t>kk_3170960220</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01021996968</t>
+          <t>01087729278</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -6311,22 +6311,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kk_3728489315</t>
+          <t>kk_4748122429</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01088859514</t>
+          <t>01089229240</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -6339,22 +6339,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>nexen1974a</t>
+          <t>kk_4545437798</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01055782215</t>
+          <t>01021996968</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -6367,22 +6367,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_4648812045</t>
+          <t>kk_3728489315</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01045190963</t>
+          <t>01088859514</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -6395,17 +6395,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_3621695729</t>
+          <t>nexen1974a</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01053495037</t>
+          <t>01055782215</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6423,12 +6423,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kk_4789987921</t>
+          <t>kk_4648812045</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01053009139</t>
+          <t>01045190963</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -6451,12 +6451,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>lov2jjin</t>
+          <t>kk_3621695729</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01087038707</t>
+          <t>01053495037</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -6479,12 +6479,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>jakelee</t>
+          <t>kk_4789987921</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01027223531</t>
+          <t>01053009139</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -6507,12 +6507,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kk_4391641739</t>
+          <t>lov2jjin</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01091994491</t>
+          <t>01087038707</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6535,12 +6535,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kk_2873620176</t>
+          <t>jakelee</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01029480082</t>
+          <t>01027223531</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6563,12 +6563,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kk_4660550146</t>
+          <t>kk_4391641739</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01022238698</t>
+          <t>01091994491</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -6591,22 +6591,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kji5472</t>
+          <t>kk_2873620176</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01022054672</t>
+          <t>01029480082</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -6619,12 +6619,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_4660550146</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01022238698</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -6647,12 +6647,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kk_3260158755</t>
+          <t>kji5472</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01038984931</t>
+          <t>01022054672</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6675,12 +6675,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>shon5072</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01095777956</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -6703,22 +6703,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>mijlove</t>
+          <t>kk_3260158755</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01092285002</t>
+          <t>01038984931</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -6731,22 +6731,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>nicole</t>
+          <t>shon5072</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01083410822</t>
+          <t>01095777956</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -6759,22 +6759,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>yahoo0402</t>
+          <t>mijlove</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01050319361</t>
+          <t>01092285002</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -6787,22 +6787,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kk_4848752733</t>
+          <t>nicole</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01090534422</t>
+          <t>01083410822</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>pmax</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -6815,22 +6815,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>kk_4825328334</t>
+          <t>yahoo0402</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01022625558</t>
+          <t>01050319361</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -6843,12 +6843,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>kk_4711817746</t>
+          <t>kk_4848752733</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01073740979</t>
+          <t>01090534422</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -6871,22 +6871,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>kk_3914085758</t>
+          <t>kk_4825328334</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01031872338</t>
+          <t>01022625558</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -6899,12 +6899,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_4896487866</t>
+          <t>kk_4711817746</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01050400311</t>
+          <t>01073740979</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -6927,12 +6927,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>kk_3227570959</t>
+          <t>kk_3914085758</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01028169084</t>
+          <t>01031872338</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -6955,12 +6955,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>segyung2</t>
+          <t>kk_4896487866</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01089808520</t>
+          <t>01050400311</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -6983,22 +6983,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sclpion</t>
+          <t>kk_3227570959</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01088740653</t>
+          <t>01028169084</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -7011,12 +7011,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>segyung2</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01089808520</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7039,12 +7039,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>kk_3607933321</t>
+          <t>sclpion</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01035122820</t>
+          <t>01088740653</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7067,22 +7067,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>kk_4481949959</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01077434037</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -7095,12 +7095,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kk_4860720956</t>
+          <t>kk_3607933321</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01056709617</t>
+          <t>01035122820</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0423_EFW</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7123,12 +7123,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>kk_4467979962</t>
+          <t>kk_4481949959</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01037751563</t>
+          <t>01077434037</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7151,22 +7151,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>kk_5009517640</t>
+          <t>kk_4860720956</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01090817520</t>
+          <t>01056709617</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>KAKAO_CH_MESSAGE_0423_EFW</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7179,22 +7179,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_2770056564</t>
+          <t>kk_4467979962</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01097609451</t>
+          <t>01037751563</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7207,22 +7207,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ryeol1004</t>
+          <t>kk_5009517640</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01087308928</t>
+          <t>01090817520</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -7235,12 +7235,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>chk1987</t>
+          <t>kk_2770056564</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01067608088</t>
+          <t>01097609451</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7263,22 +7263,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>kk_4520208596</t>
+          <t>ryeol1004</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01025741462</t>
+          <t>01087308928</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -7291,22 +7291,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kk_3182043466</t>
+          <t>chk1987</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01092562936</t>
+          <t>01067608088</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -7319,22 +7319,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>kk_4520208596</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01025741462</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -7347,22 +7347,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>pearl52</t>
+          <t>kk_3182043466</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01050351018</t>
+          <t>01092562936</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -7375,22 +7375,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>kk_4929043811</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01037904341</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -7403,12 +7403,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>kk_4673119425</t>
+          <t>pearl52</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01085632266</t>
+          <t>01050351018</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>naversa_pc</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>kk_3639045388</t>
+          <t>kk_4929043811</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01064334743</t>
+          <t>01037904341</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -7459,12 +7459,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>gbj20022002</t>
+          <t>kk_4673119425</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01053509041</t>
+          <t>01085632266</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naversa_pc</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -7487,22 +7487,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>kk_4744667185</t>
+          <t>kk_3639045388</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01047226521</t>
+          <t>01064334743</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -7515,22 +7515,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_4744667185</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01047226521</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -7543,22 +7543,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kk_3337408762</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01095768922</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -7571,22 +7571,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kk_4650374928</t>
+          <t>kk_3337408762</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01086157107</t>
+          <t>01095768922</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -7599,22 +7599,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kk_3388290079</t>
+          <t>kk_4650374928</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01083191557</t>
+          <t>01086157107</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>kakao_ch_message_0325_s26new_cta</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -7627,12 +7627,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ysj1127</t>
+          <t>kk_3388290079</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01071109388</t>
+          <t>01083191557</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>kakao_ch_message_0325_s26new_cta</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -7655,12 +7655,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>pyhlove53</t>
+          <t>ysj1127</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01094031004</t>
+          <t>01071109388</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -7683,22 +7683,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>honor181</t>
+          <t>pyhlove53</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01046301211</t>
+          <t>01094031004</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -7711,12 +7711,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ddolme</t>
+          <t>honor181</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01050040644</t>
+          <t>01046301211</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -7739,22 +7739,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kk_4416125651</t>
+          <t>ddolme</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01052177552</t>
+          <t>01050040644</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -7767,22 +7767,22 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>bbjj2000</t>
+          <t>kk_4416125651</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01035218300</t>
+          <t>01052177552</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -7795,22 +7795,22 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>sih92</t>
+          <t>bbjj2000</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01029623377</t>
+          <t>01035218300</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -7823,22 +7823,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>kk_3835565251</t>
+          <t>sih92</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01027409786</t>
+          <t>01029623377</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -7851,12 +7851,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>kingjo</t>
+          <t>kk_3835565251</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01062660099</t>
+          <t>01027409786</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -7879,12 +7879,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>guswo7310</t>
+          <t>kingjo</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01044712040</t>
+          <t>01062660099</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -7907,22 +7907,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>kk_2807327385</t>
+          <t>guswo7310</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01038584194</t>
+          <t>01044712040</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -7935,22 +7935,22 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>kk_3639576029</t>
+          <t>kk_2807327385</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01063967727</t>
+          <t>01038584194</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -7963,22 +7963,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>kk_4936216487</t>
+          <t>kk_3639576029</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01045751707</t>
+          <t>01063967727</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -7991,12 +7991,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>pivy87</t>
+          <t>kk_4936216487</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01063819999</t>
+          <t>01045751707</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -8019,12 +8019,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>kk_2826668268</t>
+          <t>pivy87</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01074843858</t>
+          <t>01063819999</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -8047,17 +8047,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>joontak</t>
+          <t>kk_2826668268</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01088917848</t>
+          <t>01074843858</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -8075,22 +8075,22 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>kk_4635961106</t>
+          <t>joontak</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01027884773</t>
+          <t>01088917848</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -8103,22 +8103,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>kk_3949518630</t>
+          <t>kk_4635961106</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01033587883</t>
+          <t>01027884773</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -8131,12 +8131,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>hyundoart</t>
+          <t>kk_3949518630</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01096853214</t>
+          <t>01033587883</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -8159,12 +8159,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>kk_4600202212</t>
+          <t>hyundoart</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01095679374</t>
+          <t>01096853214</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1024_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -8187,22 +8187,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>kk_4503210270</t>
+          <t>kk_4600202212</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01071098993</t>
+          <t>01095679374</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1024_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -8215,12 +8215,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>kk_4481940140</t>
+          <t>kk_4503210270</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01065676272</t>
+          <t>01071098993</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>[PF_SA] 컬럼비아 상시</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -8243,12 +8243,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>kk_4750629166</t>
+          <t>kk_4481940140</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01065748515</t>
+          <t>01065676272</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF_SA] 컬럼비아 상시</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -8271,22 +8271,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>kk_4746271433</t>
+          <t>kk_4750629166</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01088977839</t>
+          <t>01065748515</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -8299,12 +8299,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>mondora</t>
+          <t>kk_4746271433</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01026379832</t>
+          <t>01088977839</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>EDM_0305</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -8327,22 +8327,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>kk_4493450118</t>
+          <t>mondora</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01077566800</t>
+          <t>01026379832</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0305</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -8355,22 +8355,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>kk_4869187470</t>
+          <t>kk_4493450118</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01064823221</t>
+          <t>01077566800</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -8383,22 +8383,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>kk_3722415174</t>
+          <t>kk_4869187470</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01036589994</t>
+          <t>01064823221</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8411,12 +8411,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>loxolist</t>
+          <t>kk_3722415174</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01068552419</t>
+          <t>01036589994</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -8439,22 +8439,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>oh8314</t>
+          <t>loxolist</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01090595921</t>
+          <t>01068552419</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>lf</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
@@ -8467,22 +8467,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>kk_3825664300</t>
+          <t>oh8314</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01040323452</t>
+          <t>01090595921</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>lf</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
@@ -8495,22 +8495,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ustar777</t>
+          <t>kk_3825664300</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01027424281</t>
+          <t>01040323452</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
@@ -8523,22 +8523,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>cjonghak</t>
+          <t>ustar777</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01090444081</t>
+          <t>01027424281</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>EDM_0317</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -8551,22 +8551,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>kk_3500501777</t>
+          <t>cjonghak</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01038347573</t>
+          <t>01090444081</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>EDM_0317</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -8579,12 +8579,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>merhen</t>
+          <t>kk_3500501777</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01025129134</t>
+          <t>01038347573</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -12331,12 +12331,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>kk_4611877390</t>
+          <t>kk_3440880252</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>01034010575</t>
+          <t>01023828239</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>demendgen</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
@@ -12359,12 +12359,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>kk_3440880252</t>
+          <t>kk_4611877390</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>01023828239</t>
+          <t>01034010575</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>demendgen</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
@@ -13003,22 +13003,22 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>kk_3777466040</t>
+          <t>kk_4742048286</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>01088374115</t>
+          <t>01046424731</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -13031,22 +13031,22 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>kk_4742048286</t>
+          <t>kk_3777466040</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>01046424731</t>
+          <t>01088374115</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
@@ -13087,12 +13087,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>kk_4305225948</t>
+          <t>ahnnavy</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>01097745190</t>
+          <t>01045624300</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
@@ -13115,12 +13115,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ahnnavy</t>
+          <t>kk_4305225948</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>01045624300</t>
+          <t>01097745190</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -14767,12 +14767,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>kk_3333111023</t>
+          <t>starpos9</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>01046548483</t>
+          <t>01086475152</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -14795,12 +14795,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>starpos9</t>
+          <t>kk_3333111023</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>01086475152</t>
+          <t>01046548483</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -18099,22 +18099,22 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>kk_4705329623</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01064926793</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E632" t="inlineStr"/>
@@ -18127,22 +18127,22 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>kk_5002711068</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>01091991969</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E633" t="inlineStr"/>
@@ -18155,12 +18155,12 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>kk_4705329623</t>
+          <t>kk_5002711068</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>01064926793</t>
+          <t>01091991969</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E634" t="inlineStr"/>
@@ -19835,22 +19835,22 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E694" t="inlineStr"/>
@@ -19863,22 +19863,22 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E695" t="inlineStr"/>
@@ -19947,12 +19947,12 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>kk_4725433749</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>01096687926</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E698" t="inlineStr"/>
@@ -19975,12 +19975,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4725433749</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01096687926</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E699" t="inlineStr"/>
@@ -20479,12 +20479,12 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>kk_4883722134</t>
+          <t>kk_4202144050</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>01043573603</t>
+          <t>01085708380</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0507_LIGHTBACKPACK</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E717" t="inlineStr"/>
@@ -20507,12 +20507,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>kk_4202144050</t>
+          <t>kk_4883722134</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>01085708380</t>
+          <t>01043573603</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0507_LIGHTBACKPACK</t>
         </is>
       </c>
       <c r="E718" t="inlineStr"/>
@@ -21907,22 +21907,22 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>hunylee</t>
+          <t>silverjida</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>01086334375</t>
+          <t>01028180759</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E768" t="inlineStr"/>
@@ -21935,22 +21935,22 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>silverjida</t>
+          <t>hunylee</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>01028180759</t>
+          <t>01086334375</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E769" t="inlineStr"/>
@@ -22411,12 +22411,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>jokowoo</t>
+          <t>sephira</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01040299924</t>
+          <t>01041867593</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -22426,7 +22426,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E786" t="inlineStr"/>
@@ -22439,12 +22439,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>sephira</t>
+          <t>jokowoo</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>01041867593</t>
+          <t>01040299924</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E787" t="inlineStr"/>
@@ -23531,22 +23531,22 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>kk_3691186788</t>
+          <t>kk_3295287343</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>01072030738</t>
+          <t>01055787714</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E826" t="inlineStr"/>
@@ -23559,22 +23559,22 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>kk_3295287343</t>
+          <t>kk_3691186788</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>01055787714</t>
+          <t>01072030738</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E827" t="inlineStr"/>
@@ -24119,22 +24119,22 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>kk_4298043202</t>
+          <t>tesung1133</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>01047114486</t>
+          <t>01080018889</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
       <c r="E847" t="inlineStr"/>
@@ -24147,22 +24147,22 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>tesung1133</t>
+          <t>kk_4298043202</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>01080018889</t>
+          <t>01047114486</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E848" t="inlineStr"/>
@@ -24371,12 +24371,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>kk_4354536465</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>01090782401</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E856" t="inlineStr"/>
@@ -24399,12 +24399,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4354536465</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01090782401</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -24414,7 +24414,7 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E857" t="inlineStr"/>
@@ -24623,22 +24623,22 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>kk_2771972168</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>01029820030</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E865" t="inlineStr"/>
@@ -24651,22 +24651,22 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_2771972168</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01029820030</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E866" t="inlineStr"/>
@@ -24707,12 +24707,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>kk_3166693744</t>
+          <t>kk_3809928726</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>01045579380</t>
+          <t>01079193871</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -24735,12 +24735,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>kk_3166693744</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01045579380</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -24987,22 +24987,22 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>kalisuma87</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01075998784</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E878" t="inlineStr"/>
@@ -25015,22 +25015,22 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>kalisuma87</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>01075998784</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E879" t="inlineStr"/>
@@ -25295,22 +25295,22 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>kk_3421258407</t>
+          <t>pavilecolumbia</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01040887568</t>
+          <t>01052876062</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E889" t="inlineStr"/>
@@ -25323,22 +25323,22 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>pavilecolumbia</t>
+          <t>kk_3421258407</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01052876062</t>
+          <t>01040887568</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E890" t="inlineStr"/>
@@ -25631,12 +25631,12 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>kk_2825498802</t>
+          <t>jhj95</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01027817891</t>
+          <t>01031240827</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E901" t="inlineStr"/>
@@ -25659,12 +25659,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>khyoon99</t>
+          <t>kk_3957117484</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01044153686</t>
+          <t>01042204013</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -25674,7 +25674,7 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E902" t="inlineStr"/>
@@ -25687,12 +25687,12 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>jhj95</t>
+          <t>kk_2825498802</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>01031240827</t>
+          <t>01027817891</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E903" t="inlineStr"/>
@@ -25715,12 +25715,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>kk_3957117484</t>
+          <t>khyoon99</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>01042204013</t>
+          <t>01044153686</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -25730,7 +25730,7 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E904" t="inlineStr"/>

--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -451,27 +451,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>c100374</t>
+          <t>welko33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01063328561</t>
+          <t>01052950560</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EDM_0209_LIGHTBAG</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>Heather Canyon II Jacket</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5387,12 +5387,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>fkilove</t>
+          <t>ace1331</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01080118915</t>
+          <t>01033906903</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>EDM_0502</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -5415,12 +5415,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ace1331</t>
+          <t>fkilove</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01033906903</t>
+          <t>01080118915</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EDM_0502</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -11603,22 +11603,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>aurora1530</t>
+          <t>jaeho86</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>01090756922</t>
+          <t>01091199057</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EDM_0317</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -11631,22 +11631,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>jaeho86</t>
+          <t>aurora1530</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>01091199057</t>
+          <t>01090756922</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>EDM_0317</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
@@ -12751,22 +12751,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>kk_4486967764</t>
+          <t>kk_3181390163</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>01095303556</t>
+          <t>01081430435</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -12779,22 +12779,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>kk_3181390163</t>
+          <t>kk_4486967764</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>01081430435</t>
+          <t>01095303556</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -13507,12 +13507,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>kk_3377297415</t>
+          <t>kk_3866704464</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>01088479524</t>
+          <t>01096848789</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E468" t="inlineStr"/>
@@ -13535,12 +13535,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>kk_3866704464</t>
+          <t>kk_3377297415</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>01096848789</t>
+          <t>01088479524</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E469" t="inlineStr"/>
@@ -14319,12 +14319,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>kk_3846090083</t>
+          <t>kk_4850097780</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>01062091126</t>
+          <t>01053956505</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E497" t="inlineStr"/>
@@ -14347,12 +14347,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>kk_4850097780</t>
+          <t>kk_3846090083</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>01053956505</t>
+          <t>01062091126</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E498" t="inlineStr"/>
@@ -14543,22 +14543,22 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>lha0509</t>
+          <t>designjy</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>01099215769</t>
+          <t>01035455888</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>EDM_0512</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E505" t="inlineStr"/>
@@ -14571,22 +14571,22 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>designjy</t>
+          <t>lha0509</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>01035455888</t>
+          <t>01099215769</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>EDM_0512</t>
         </is>
       </c>
       <c r="E506" t="inlineStr"/>
@@ -14767,12 +14767,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>starpos9</t>
+          <t>kk_3333111023</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>01086475152</t>
+          <t>01046548483</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -14795,12 +14795,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>kk_3333111023</t>
+          <t>starpos9</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>01046548483</t>
+          <t>01086475152</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -16447,12 +16447,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>kk_4912807536</t>
+          <t>pjh5540</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>01046055617</t>
+          <t>01085559978</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>gdn</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E573" t="inlineStr"/>
@@ -16475,12 +16475,12 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>pjh5540</t>
+          <t>kk_4912807536</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>01085559978</t>
+          <t>01046055617</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>gdn</t>
         </is>
       </c>
       <c r="E574" t="inlineStr"/>
@@ -16643,22 +16643,22 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>kk_4709923210</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>01096124789</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E580" t="inlineStr"/>
@@ -16671,22 +16671,22 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_4709923210</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01096124789</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E581" t="inlineStr"/>
@@ -18099,12 +18099,12 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>kk_5002711068</t>
+          <t>kk_4705329623</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>01091991969</t>
+          <t>01064926793</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E632" t="inlineStr"/>
@@ -18127,22 +18127,22 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>kk_5002711068</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01091991969</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E633" t="inlineStr"/>
@@ -18155,22 +18155,22 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>kk_4705329623</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>01064926793</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E634" t="inlineStr"/>
@@ -19751,12 +19751,12 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>kk_3786745879</t>
+          <t>kk_4318436675</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>01093675013</t>
+          <t>01031176390</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E691" t="inlineStr"/>
@@ -19779,12 +19779,12 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>kk_4318436675</t>
+          <t>kk_3786745879</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>01031176390</t>
+          <t>01093675013</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E692" t="inlineStr"/>
@@ -19835,22 +19835,22 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E694" t="inlineStr"/>
@@ -19863,22 +19863,22 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E695" t="inlineStr"/>
@@ -19947,12 +19947,12 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4725433749</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01096687926</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E698" t="inlineStr"/>
@@ -19975,12 +19975,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>kk_4725433749</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>01096687926</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E699" t="inlineStr"/>
@@ -20003,12 +20003,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>kk_3911965677</t>
+          <t>kk_4455109384</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>01029276124</t>
+          <t>01025222519</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -20031,12 +20031,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>kk_4455109384</t>
+          <t>kk_3911965677</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>01025222519</t>
+          <t>01029276124</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -22103,22 +22103,22 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>kk_4857948457</t>
+          <t>lovelybeib</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>01058380760</t>
+          <t>01040981902</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E775" t="inlineStr"/>
@@ -22131,22 +22131,22 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>lovelybeib</t>
+          <t>kk_4857948457</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>01040981902</t>
+          <t>01058380760</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E776" t="inlineStr"/>
@@ -22411,12 +22411,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>sephira</t>
+          <t>jokowoo</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01041867593</t>
+          <t>01040299924</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -22426,7 +22426,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E786" t="inlineStr"/>
@@ -22439,12 +22439,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>jokowoo</t>
+          <t>sephira</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>01040299924</t>
+          <t>01041867593</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E787" t="inlineStr"/>
@@ -23531,22 +23531,22 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>kk_3295287343</t>
+          <t>kk_3691186788</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>01055787714</t>
+          <t>01072030738</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E826" t="inlineStr"/>
@@ -23559,22 +23559,22 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>kk_3691186788</t>
+          <t>kk_3295287343</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>01072030738</t>
+          <t>01055787714</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E827" t="inlineStr"/>
@@ -23615,12 +23615,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>kk_3179837389</t>
+          <t>kk_4582648301</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>01089490421</t>
+          <t>01040451815</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -23630,7 +23630,7 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>0803_SUMMER_LAST_CHANCE</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E829" t="inlineStr"/>
@@ -23643,12 +23643,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>kk_4582648301</t>
+          <t>kk_3179837389</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>01040451815</t>
+          <t>01089490421</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>0803_SUMMER_LAST_CHANCE</t>
         </is>
       </c>
       <c r="E830" t="inlineStr"/>
@@ -23783,12 +23783,12 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>kk_4604844467</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>01045678553</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E835" t="inlineStr"/>
@@ -23811,12 +23811,12 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>kk_4604844467</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01045678553</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E836" t="inlineStr"/>
@@ -24511,12 +24511,12 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>kk_4614679325</t>
+          <t>leeyh015</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>01063402986</t>
+          <t>01020785413</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E861" t="inlineStr"/>
@@ -24539,12 +24539,12 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>leeyh015</t>
+          <t>kk_4614679325</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>01020785413</t>
+          <t>01063402986</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E862" t="inlineStr"/>
@@ -24623,22 +24623,22 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_2771972168</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01029820030</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E865" t="inlineStr"/>
@@ -24651,22 +24651,22 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>kk_2771972168</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>01029820030</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E866" t="inlineStr"/>
@@ -24707,12 +24707,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>kk_3166693744</t>
+          <t>kk_3809928726</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>01045579380</t>
+          <t>01079193871</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -24735,12 +24735,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>kk_3166693744</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01045579380</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -24987,22 +24987,22 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>kalisuma87</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01075998784</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E878" t="inlineStr"/>
@@ -25015,22 +25015,22 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>kalisuma87</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>01075998784</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E879" t="inlineStr"/>
@@ -25239,12 +25239,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>kk_4376700680</t>
+          <t>kk_4864045300</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>01047096832</t>
+          <t>01089985309</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0425_FAMILYSALE</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E887" t="inlineStr"/>
@@ -25267,12 +25267,12 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>kk_4864045300</t>
+          <t>kk_4376700680</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>01089985309</t>
+          <t>01047096832</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -25282,7 +25282,7 @@
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0425_FAMILYSALE</t>
         </is>
       </c>
       <c r="E888" t="inlineStr"/>
@@ -25295,22 +25295,22 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>pavilecolumbia</t>
+          <t>kk_3421258407</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01052876062</t>
+          <t>01040887568</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E889" t="inlineStr"/>
@@ -25323,22 +25323,22 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>kk_3421258407</t>
+          <t>pavilecolumbia</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01040887568</t>
+          <t>01052876062</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E890" t="inlineStr"/>
@@ -25491,22 +25491,22 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>kk_4286220576</t>
+          <t>kk_4977819786</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>01053587782</t>
+          <t>01063257991</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_seasonoff</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E896" t="inlineStr"/>
@@ -25519,22 +25519,22 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>kk_4977819786</t>
+          <t>kk_4286220576</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>01063257991</t>
+          <t>01053587782</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_200416_seasonoff</t>
         </is>
       </c>
       <c r="E897" t="inlineStr"/>
@@ -25631,12 +25631,12 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>kk_3957117484</t>
+          <t>kk_2825498802</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01042204013</t>
+          <t>01027817891</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E901" t="inlineStr"/>
@@ -25659,12 +25659,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>kk_2825498802</t>
+          <t>jhj95</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01027817891</t>
+          <t>01031240827</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -25674,7 +25674,7 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E902" t="inlineStr"/>
@@ -25715,12 +25715,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>jhj95</t>
+          <t>kk_3957117484</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>01031240827</t>
+          <t>01042204013</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -25730,7 +25730,7 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E904" t="inlineStr"/>
@@ -25827,12 +25827,12 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>kk_3467972511</t>
+          <t>tae12080</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>01031899111</t>
+          <t>01093170063</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E908" t="inlineStr"/>
@@ -25855,12 +25855,12 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>tae12080</t>
+          <t>kk_3467972511</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>01093170063</t>
+          <t>01031899111</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E909" t="inlineStr"/>

--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -12331,12 +12331,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>kk_3440880252</t>
+          <t>kk_4611877390</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>01023828239</t>
+          <t>01034010575</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>demendgen</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
@@ -12359,12 +12359,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>kk_4611877390</t>
+          <t>kk_3440880252</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>01034010575</t>
+          <t>01023828239</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>demendgen</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
@@ -13087,12 +13087,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>kk_4305225948</t>
+          <t>ahnnavy</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>01097745190</t>
+          <t>01045624300</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
@@ -13115,12 +13115,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ahnnavy</t>
+          <t>kk_4305225948</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>01045624300</t>
+          <t>01097745190</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -15635,12 +15635,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>youl29</t>
+          <t>kk_4602095632</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>01050134121</t>
+          <t>01033213747</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15663,12 +15663,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>kk_4602095632</t>
+          <t>youl29</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>01033213747</t>
+          <t>01050134121</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -16447,12 +16447,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>pjh5540</t>
+          <t>kk_4912807536</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>01085559978</t>
+          <t>01046055617</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>gdn</t>
         </is>
       </c>
       <c r="E573" t="inlineStr"/>
@@ -16475,12 +16475,12 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>kk_4912807536</t>
+          <t>pjh5540</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>01046055617</t>
+          <t>01085559978</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>gdn</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E574" t="inlineStr"/>
@@ -16643,22 +16643,22 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_4709923210</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01096124789</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E580" t="inlineStr"/>
@@ -16671,22 +16671,22 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>kk_4709923210</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>01096124789</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E581" t="inlineStr"/>
@@ -16699,12 +16699,12 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>likeessay</t>
+          <t>kk_2874121871</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>01087636086</t>
+          <t>01040870367</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E582" t="inlineStr"/>
@@ -16727,12 +16727,12 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>kk_2874121871</t>
+          <t>likeessay</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>01040870367</t>
+          <t>01087636086</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E583" t="inlineStr"/>
@@ -18099,22 +18099,22 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>kk_4705329623</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>01064926793</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E632" t="inlineStr"/>
@@ -18155,22 +18155,22 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>kk_4705329623</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01064926793</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E634" t="inlineStr"/>
@@ -19751,12 +19751,12 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>kk_4318436675</t>
+          <t>kk_3786745879</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>01031176390</t>
+          <t>01093675013</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E691" t="inlineStr"/>
@@ -19779,12 +19779,12 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>kk_3786745879</t>
+          <t>kk_4318436675</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>01093675013</t>
+          <t>01031176390</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E692" t="inlineStr"/>
@@ -20003,12 +20003,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>kk_4455109384</t>
+          <t>kk_3911965677</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>01025222519</t>
+          <t>01029276124</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -20031,12 +20031,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>kk_3911965677</t>
+          <t>kk_4455109384</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>01029276124</t>
+          <t>01025222519</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -20675,22 +20675,22 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>cyclepm</t>
+          <t>kk_4747397154</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>01027101838</t>
+          <t>01052568046</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>LMS_ECOM_1110_Raffle</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E724" t="inlineStr"/>
@@ -20703,22 +20703,22 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>kk_4747397154</t>
+          <t>kk_4588287948</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>01052568046</t>
+          <t>01091651067</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E725" t="inlineStr"/>
@@ -20731,22 +20731,22 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>kk_4588287948</t>
+          <t>cyclepm</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>01091651067</t>
+          <t>01027101838</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_1110_Raffle</t>
         </is>
       </c>
       <c r="E726" t="inlineStr"/>
@@ -21907,22 +21907,22 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>silverjida</t>
+          <t>hunylee</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>01028180759</t>
+          <t>01086334375</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E768" t="inlineStr"/>
@@ -21935,22 +21935,22 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>hunylee</t>
+          <t>silverjida</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>01086334375</t>
+          <t>01028180759</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E769" t="inlineStr"/>
@@ -22411,12 +22411,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>jokowoo</t>
+          <t>sephira</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01040299924</t>
+          <t>01041867593</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -22426,7 +22426,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E786" t="inlineStr"/>
@@ -22439,12 +22439,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>sephira</t>
+          <t>jokowoo</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>01041867593</t>
+          <t>01040299924</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E787" t="inlineStr"/>
@@ -23531,22 +23531,22 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>kk_3691186788</t>
+          <t>kk_3295287343</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>01072030738</t>
+          <t>01055787714</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E826" t="inlineStr"/>
@@ -23559,22 +23559,22 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>kk_3295287343</t>
+          <t>kk_3691186788</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>01055787714</t>
+          <t>01072030738</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E827" t="inlineStr"/>
@@ -23615,12 +23615,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>kk_4582648301</t>
+          <t>kk_3179837389</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>01040451815</t>
+          <t>01089490421</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -23630,7 +23630,7 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>0803_SUMMER_LAST_CHANCE</t>
         </is>
       </c>
       <c r="E829" t="inlineStr"/>
@@ -23643,12 +23643,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>kk_3179837389</t>
+          <t>kk_4582648301</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>01089490421</t>
+          <t>01040451815</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>0803_SUMMER_LAST_CHANCE</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E830" t="inlineStr"/>
@@ -24119,22 +24119,22 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>kk_4298043202</t>
+          <t>tesung1133</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>01047114486</t>
+          <t>01080018889</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
       <c r="E847" t="inlineStr"/>
@@ -24147,22 +24147,22 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>tesung1133</t>
+          <t>kk_4298043202</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>01080018889</t>
+          <t>01047114486</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E848" t="inlineStr"/>
@@ -24371,12 +24371,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>kk_4354536465</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>01090782401</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E856" t="inlineStr"/>
@@ -24399,12 +24399,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4354536465</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01090782401</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -24414,7 +24414,7 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E857" t="inlineStr"/>
@@ -24511,12 +24511,12 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>leeyh015</t>
+          <t>kk_4614679325</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>01020785413</t>
+          <t>01063402986</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E861" t="inlineStr"/>
@@ -24539,12 +24539,12 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>kk_4614679325</t>
+          <t>leeyh015</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>01063402986</t>
+          <t>01020785413</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E862" t="inlineStr"/>
@@ -24707,12 +24707,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>kk_3166693744</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01045579380</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -24735,12 +24735,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>kk_3166693744</t>
+          <t>kk_3809928726</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>01045579380</t>
+          <t>01079193871</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -24987,22 +24987,22 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>kalisuma87</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>01075998784</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E878" t="inlineStr"/>
@@ -25015,22 +25015,22 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>kalisuma87</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01075998784</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E879" t="inlineStr"/>
@@ -25295,22 +25295,22 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>kk_3421258407</t>
+          <t>pavilecolumbia</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01040887568</t>
+          <t>01052876062</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E889" t="inlineStr"/>
@@ -25323,22 +25323,22 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>pavilecolumbia</t>
+          <t>kk_3421258407</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01052876062</t>
+          <t>01040887568</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E890" t="inlineStr"/>
@@ -25491,22 +25491,22 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>kk_4977819786</t>
+          <t>kk_4286220576</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>01063257991</t>
+          <t>01053587782</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_200416_seasonoff</t>
         </is>
       </c>
       <c r="E896" t="inlineStr"/>
@@ -25519,22 +25519,22 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>kk_4286220576</t>
+          <t>kk_4977819786</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>01053587782</t>
+          <t>01063257991</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_seasonoff</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E897" t="inlineStr"/>
@@ -25631,12 +25631,12 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>kk_2825498802</t>
+          <t>kk_3957117484</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01027817891</t>
+          <t>01042204013</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E901" t="inlineStr"/>
@@ -25659,12 +25659,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>jhj95</t>
+          <t>khyoon99</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01031240827</t>
+          <t>01044153686</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -25687,12 +25687,12 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>khyoon99</t>
+          <t>jhj95</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>01044153686</t>
+          <t>01031240827</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -25715,12 +25715,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>kk_3957117484</t>
+          <t>kk_2825498802</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>01042204013</t>
+          <t>01027817891</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -25730,7 +25730,7 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E904" t="inlineStr"/>

--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -5387,12 +5387,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>fkilove</t>
+          <t>ace1331</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01080118915</t>
+          <t>01033906903</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>EDM_0502</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -5415,12 +5415,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ace1331</t>
+          <t>fkilove</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01033906903</t>
+          <t>01080118915</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EDM_0502</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -11603,22 +11603,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>aurora1530</t>
+          <t>jaeho86</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>01090756922</t>
+          <t>01091199057</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EDM_0317</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -11631,22 +11631,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>jaeho86</t>
+          <t>aurora1530</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>01091199057</t>
+          <t>01090756922</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>EDM_0317</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
@@ -12331,12 +12331,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>kk_3440880252</t>
+          <t>kk_4611877390</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>01023828239</t>
+          <t>01034010575</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>demendgen</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
@@ -12359,12 +12359,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>kk_4611877390</t>
+          <t>kk_3440880252</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>01034010575</t>
+          <t>01023828239</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>demendgen</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
@@ -13003,22 +13003,22 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>kk_4742048286</t>
+          <t>kk_3777466040</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>01046424731</t>
+          <t>01088374115</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -13031,22 +13031,22 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>kk_3777466040</t>
+          <t>kk_4742048286</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>01088374115</t>
+          <t>01046424731</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
@@ -13087,12 +13087,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>kk_4305225948</t>
+          <t>ahnnavy</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>01097745190</t>
+          <t>01045624300</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
@@ -13115,12 +13115,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ahnnavy</t>
+          <t>kk_4305225948</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>01045624300</t>
+          <t>01097745190</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -13507,12 +13507,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>kk_3866704464</t>
+          <t>kk_3377297415</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>01096848789</t>
+          <t>01088479524</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E468" t="inlineStr"/>
@@ -13535,12 +13535,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>kk_3377297415</t>
+          <t>kk_3866704464</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>01088479524</t>
+          <t>01096848789</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E469" t="inlineStr"/>
@@ -14319,12 +14319,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>kk_4850097780</t>
+          <t>kk_3846090083</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>01053956505</t>
+          <t>01062091126</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E497" t="inlineStr"/>
@@ -14347,12 +14347,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>kk_3846090083</t>
+          <t>kk_4850097780</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>01062091126</t>
+          <t>01053956505</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E498" t="inlineStr"/>
@@ -14543,22 +14543,22 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>lha0509</t>
+          <t>designjy</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>01099215769</t>
+          <t>01035455888</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>EDM_0512</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E505" t="inlineStr"/>
@@ -14571,22 +14571,22 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>designjy</t>
+          <t>lha0509</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>01035455888</t>
+          <t>01099215769</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>EDM_0512</t>
         </is>
       </c>
       <c r="E506" t="inlineStr"/>
@@ -15635,12 +15635,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>kk_4602095632</t>
+          <t>youl29</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>01033213747</t>
+          <t>01050134121</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15663,12 +15663,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>youl29</t>
+          <t>kk_4602095632</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>01050134121</t>
+          <t>01033213747</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -16643,22 +16643,22 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_4709923210</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01096124789</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E580" t="inlineStr"/>
@@ -16671,22 +16671,22 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>kk_4709923210</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>01096124789</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E581" t="inlineStr"/>
@@ -16699,12 +16699,12 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>kk_2874121871</t>
+          <t>likeessay</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>01040870367</t>
+          <t>01087636086</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E582" t="inlineStr"/>
@@ -16727,12 +16727,12 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>likeessay</t>
+          <t>kk_2874121871</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>01087636086</t>
+          <t>01040870367</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E583" t="inlineStr"/>
@@ -18127,12 +18127,12 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>kk_5002711068</t>
+          <t>kk_4705329623</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>01091991969</t>
+          <t>01064926793</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E633" t="inlineStr"/>
@@ -18155,12 +18155,12 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>kk_4705329623</t>
+          <t>kk_5002711068</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>01064926793</t>
+          <t>01091991969</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E634" t="inlineStr"/>
@@ -18323,22 +18323,22 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>ing106</t>
+          <t>kk_3490560323</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>01099047122</t>
+          <t>01035493044</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_CH_MESSAGE_0423_EFW</t>
         </is>
       </c>
       <c r="E640" t="inlineStr"/>
@@ -18351,22 +18351,22 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>kk_3490560323</t>
+          <t>ing106</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>01035493044</t>
+          <t>01099047122</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0423_EFW</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E641" t="inlineStr"/>
@@ -19751,12 +19751,12 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>kk_3786745879</t>
+          <t>kk_4318436675</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>01093675013</t>
+          <t>01031176390</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E691" t="inlineStr"/>
@@ -19779,12 +19779,12 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>kk_4318436675</t>
+          <t>kk_3786745879</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>01031176390</t>
+          <t>01093675013</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E692" t="inlineStr"/>
@@ -19835,22 +19835,22 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E694" t="inlineStr"/>
@@ -19863,22 +19863,22 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E695" t="inlineStr"/>
@@ -20479,12 +20479,12 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>kk_4202144050</t>
+          <t>kk_4883722134</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>01085708380</t>
+          <t>01043573603</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0507_LIGHTBACKPACK</t>
         </is>
       </c>
       <c r="E717" t="inlineStr"/>
@@ -20507,12 +20507,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>kk_4883722134</t>
+          <t>kk_4202144050</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>01043573603</t>
+          <t>01085708380</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0507_LIGHTBACKPACK</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E718" t="inlineStr"/>
@@ -22103,22 +22103,22 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>lovelybeib</t>
+          <t>kk_4857948457</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>01040981902</t>
+          <t>01058380760</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E775" t="inlineStr"/>
@@ -22131,22 +22131,22 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>kk_4857948457</t>
+          <t>lovelybeib</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>01058380760</t>
+          <t>01040981902</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E776" t="inlineStr"/>
@@ -22411,12 +22411,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>jokowoo</t>
+          <t>sephira</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01040299924</t>
+          <t>01041867593</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -22426,7 +22426,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E786" t="inlineStr"/>
@@ -22439,12 +22439,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>sephira</t>
+          <t>jokowoo</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>01041867593</t>
+          <t>01040299924</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E787" t="inlineStr"/>
@@ -23531,22 +23531,22 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>kk_3691186788</t>
+          <t>kk_3295287343</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>01072030738</t>
+          <t>01055787714</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E826" t="inlineStr"/>
@@ -23559,22 +23559,22 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>kk_3295287343</t>
+          <t>kk_3691186788</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>01055787714</t>
+          <t>01072030738</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E827" t="inlineStr"/>
@@ -23615,12 +23615,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>kk_3179837389</t>
+          <t>kk_4582648301</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>01089490421</t>
+          <t>01040451815</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -23630,7 +23630,7 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>0803_SUMMER_LAST_CHANCE</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E829" t="inlineStr"/>
@@ -23643,12 +23643,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>kk_4582648301</t>
+          <t>kk_3179837389</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>01040451815</t>
+          <t>01089490421</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>0803_SUMMER_LAST_CHANCE</t>
         </is>
       </c>
       <c r="E830" t="inlineStr"/>
@@ -23783,12 +23783,12 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>kk_4604844467</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01045678553</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E835" t="inlineStr"/>
@@ -23811,12 +23811,12 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>kk_4604844467</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>01045678553</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E836" t="inlineStr"/>
@@ -24119,22 +24119,22 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>kk_4298043202</t>
+          <t>tesung1133</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>01047114486</t>
+          <t>01080018889</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
       <c r="E847" t="inlineStr"/>
@@ -24147,22 +24147,22 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>tesung1133</t>
+          <t>kk_4298043202</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>01080018889</t>
+          <t>01047114486</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E848" t="inlineStr"/>
@@ -24287,22 +24287,22 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>uok77</t>
+          <t>ohjeong2</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>01089602950</t>
+          <t>01034324152</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0507_EFW_STYLE2</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E853" t="inlineStr"/>
@@ -24315,22 +24315,22 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>ohjeong2</t>
+          <t>uok77</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>01034324152</t>
+          <t>01089602950</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_CH_MESSAGE_0507_EFW_STYLE2</t>
         </is>
       </c>
       <c r="E854" t="inlineStr"/>
@@ -24623,22 +24623,22 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>kk_2771972168</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>01029820030</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E865" t="inlineStr"/>
@@ -24651,22 +24651,22 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_2771972168</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01029820030</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E866" t="inlineStr"/>
@@ -24987,22 +24987,22 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>kalisuma87</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>01075998784</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E878" t="inlineStr"/>
@@ -25015,22 +25015,22 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>kalisuma87</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01075998784</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E879" t="inlineStr"/>
@@ -25239,12 +25239,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>kk_4376700680</t>
+          <t>kk_4864045300</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>01047096832</t>
+          <t>01089985309</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0425_FAMILYSALE</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E887" t="inlineStr"/>
@@ -25267,12 +25267,12 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>kk_4864045300</t>
+          <t>kk_4376700680</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>01089985309</t>
+          <t>01047096832</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -25282,7 +25282,7 @@
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0425_FAMILYSALE</t>
         </is>
       </c>
       <c r="E888" t="inlineStr"/>
@@ -25295,22 +25295,22 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>kk_3421258407</t>
+          <t>pavilecolumbia</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01040887568</t>
+          <t>01052876062</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E889" t="inlineStr"/>
@@ -25323,22 +25323,22 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>pavilecolumbia</t>
+          <t>kk_3421258407</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01052876062</t>
+          <t>01040887568</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E890" t="inlineStr"/>
@@ -25659,12 +25659,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>kk_3957117484</t>
+          <t>jhj95</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01042204013</t>
+          <t>01031240827</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -25674,7 +25674,7 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E902" t="inlineStr"/>
@@ -25715,12 +25715,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>jhj95</t>
+          <t>kk_3957117484</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>01031240827</t>
+          <t>01042204013</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -25730,7 +25730,7 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E904" t="inlineStr"/>
@@ -25827,12 +25827,12 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>tae12080</t>
+          <t>kk_3467972511</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>01093170063</t>
+          <t>01031899111</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E908" t="inlineStr"/>
@@ -25855,12 +25855,12 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>kk_3467972511</t>
+          <t>tae12080</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>01031899111</t>
+          <t>01093170063</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E909" t="inlineStr"/>
